--- a/Asignaciones/Recursos/canticos_lista.xlsx
+++ b/Asignaciones/Recursos/canticos_lista.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B163"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,1946 +429,1966 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Canción 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Las cualidades principales de Jehová</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Canción 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tu nombre es Jehová</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Canción 3</t>
+          <t>Canción 142</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tú me das fuerza, confianza y valor</t>
+          <t>Aferrémonos a nuestra esperanza</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Canción 4</t>
+          <t>Canción 94</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>“Jehová es mi Pastor”</t>
+          <t>Agradecidos por la Palabra de Dios</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canción 5</t>
+          <t>Canción 128</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Las maravillosas obras de Dios</t>
+          <t>Aguantemos hasta el fin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Canción 6</t>
+          <t>Canción 132</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los cielos proclaman la gloria de Dios</t>
+          <t>Ahora ya somos uno</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Canción 7</t>
+          <t>Canción 16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jehová es mi fuerza y mi salvación</t>
+          <t>Alabemos a Jehová por su Hijo, el Ungido</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canción 8</t>
+          <t>Canción 15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jehová es mi Refugio</t>
+          <t>Alabemos al Primogénito de Jehová</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canción 9</t>
+          <t>Canción 10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>¡Jehová es nuestro Rey!</t>
+          <t>¡Alabemos a nuestro Dios, Jehová!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Canción 10</t>
+          <t>Canción 49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>¡Alabemos a nuestro Dios, Jehová!</t>
+          <t>Alegremos el corazón de Jehová</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canción 11</t>
+          <t>Canción 109</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>La creación alaba a Jehová</t>
+          <t>Amémonos de todo corazón</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Canción 12</t>
+          <t>Canción 90</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jehová, nuestro gran Dios</t>
+          <t>Animémonos unos a otros</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Canción 13</t>
+          <t>Canción 72</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristo es nuestro modelo</t>
+          <t>Anunciaré la verdad del Reino</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Canción 14</t>
+          <t>Canción 130</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Honremos al nuevo Rey de la Tierra</t>
+          <t>Aprendamos a perdonar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Canción 15</t>
+          <t>Canción 40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alabemos al Primogénito de Jehová</t>
+          <t>¿A quién servimos?</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Canción 16</t>
+          <t>Canción 75</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alabemos a Jehová por su Hijo, el Ungido</t>
+          <t>“¡Aquí estoy, envíame!”</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canción 17</t>
+          <t>Canción 35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>“Quiero”</t>
+          <t>Asegurémonos de lo más importante</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canción 18</t>
+          <t>Canción 61</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gracias por el rescate</t>
+          <t>¡Avancen, Testigos!</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Canción 19</t>
+          <t>Canción 102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>La Cena del Señor</t>
+          <t>Ayudemos a los débiles</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canción 20</t>
+          <t>Canción 93</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Enviaste a Jesús, tu Hijo amado</t>
+          <t>Bendice nuestras reuniones</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Canción 21</t>
+          <t>Canción 160</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Busquemos primero el Reino</t>
+          <t>¡Buenas noticias!</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Canción 22</t>
+          <t>Canción 70</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>¡Que venga el Reino que Dios ha establecido!</t>
+          <t>Busquemos a los merecedores</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Canción 23</t>
+          <t>Canción 21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jehová ha empezado su gobierno</t>
+          <t>Busquemos primero el Reino</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Canción 24</t>
+          <t>Canción 34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Subamos a la montaña de Jehová</t>
+          <t>Caminaré en integridad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Canción 25</t>
+          <t>Canción 31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Una posesión especial</t>
+          <t>Camina siempre con Jehová</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Canción 26</t>
+          <t>Canción 48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>“Si lo haces por él, lo haces por mí”</t>
+          <t>Caminemos diariamente con Jehová</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Canción 27</t>
+          <t>Canción 28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>La revelación de los hijos de Dios</t>
+          <t>Cómo hacernos amigos de Jehová</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canción 28</t>
+          <t>Canción 13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cómo hacernos amigos de Jehová</t>
+          <t>Cristo es nuestro modelo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Canción 29</t>
+          <t>Canción 76</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hagamos honor a nuestro nombre</t>
+          <t>Cuéntame lo que sientes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Canción 30</t>
+          <t>Canción 36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mi Amigo, mi Padre, mi Dios</t>
+          <t>Cuidemos nuestro corazón</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Canción 31</t>
+          <t>Canción 106</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camina siempre con Jehová</t>
+          <t>Cultivemos amor verdadero</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Canción 32</t>
+          <t>Canción 73</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>¡Ponte de parte de Dios!</t>
+          <t>Danos fuerzas y valor</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Canción 33</t>
+          <t>Canción 118</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Echa sobre Dios tu carga</t>
+          <t>“Danos más fe”</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Canción 34</t>
+          <t>Canción 158</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caminaré en integridad</t>
+          <t>Danos paciencia</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Canción 35</t>
+          <t>Canción 83</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Asegurémonos de lo más importante</t>
+          <t>“De casa en casa”</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Canción 36</t>
+          <t>Canción 159</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cuidemos nuestro corazón</t>
+          <t>Demos gloria a Jehová</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Canción 37</t>
+          <t>Canción 114</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Serviré a Jehová con el corazón</t>
+          <t>Demostremos paciencia</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Canción 38</t>
+          <t>Canción 105</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jehová te cuidará</t>
+          <t>“Dios es amor”</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Canción 39</t>
+          <t>Canción 107</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Un buen nombre ante Dios</t>
+          <t>Dios nos enseñó a amar</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Canción 40</t>
+          <t>Canción 147</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>¿A quién servimos?</t>
+          <t>Dios nos promete la vida eterna</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Canción 41</t>
+          <t>Canción 145</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Padre, escucha mi oración</t>
+          <t>Dios prometió un Paraíso</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Canción 42</t>
+          <t>Canción 33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>La oración del siervo de Dios</t>
+          <t>Echa sobre Dios tu carga</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Canción 43</t>
+          <t>Canción 108</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Una oración para dar gracias a Dios</t>
+          <t>El amor leal de Jehová</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Canción 44</t>
+          <t>Canción 104</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Una súplica ferviente</t>
+          <t>El espíritu santo es un regalo de Dios</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Canción 45</t>
+          <t>Canción 110</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>“La meditación de mi corazón”</t>
+          <t>El gozo de Jehová</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Canción 46</t>
+          <t>Canción 96</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gracias, Jehová</t>
+          <t>El libro de Dios es un tesoro</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Canción 47</t>
+          <t>Canción 141</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Oremos a Dios todos los días</t>
+          <t>El maravilloso regalo de la vida</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Canción 48</t>
+          <t>Canción 78</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caminemos diariamente con Jehová</t>
+          <t>Enseñemos la Palabra de Dios</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Canción 49</t>
+          <t>Canción 20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alegremos el corazón de Jehová</t>
+          <t>Enviaste a Jesús, tu Hijo amado</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Canción 50</t>
+          <t>Canción 51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mi oración de dedicación</t>
+          <t>Estamos dedicados a Dios</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Canción 51</t>
+          <t>Canción 54</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Estamos dedicados a Dios</t>
+          <t>“Este es el camino”</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Canción 52</t>
+          <t>Canción 146</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>La dedicación cristiana</t>
+          <t>“Estoy haciendo todo nuevo”</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Canción 53</t>
+          <t>Canción 125</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hoy voy a salir a predicar</t>
+          <t>Felices los misericordiosos</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Canción 54</t>
+          <t>Canción 137</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>“Este es el camino”</t>
+          <t>Fieles, valiosas, amadas</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Canción 55</t>
+          <t>Canción 46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>¡No los temas!</t>
+          <t>Gracias, Jehová</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Canción 56</t>
+          <t>Canción 18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vive la verdad</t>
+          <t>Gracias por el rescate</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Canción 57</t>
+          <t>Canción 115</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Predicamos a toda clase de personas</t>
+          <t>Gratitud por la paciencia de Dios</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Canción 58</t>
+          <t>Canción 161</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Voy a buscar a los amigos de la paz</t>
+          <t>Hacer tu voluntad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Canción 59</t>
+          <t>Canción 29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ven a alabar a Jehová</t>
+          <t>Hagamos honor a nuestro nombre</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Canción 60</t>
+          <t>Canción 82</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hay vidas en juego</t>
+          <t>Hagamos que brille nuestra luz</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Canción 61</t>
+          <t>Canción 143</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>¡Avancen, Testigos!</t>
+          <t>¡Hay que seguir vigilantes!</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Canción 62</t>
+          <t>Canción 60</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>La nueva canción</t>
+          <t>Hay vidas en juego</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Canción 63</t>
+          <t>Canción 88</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>¡Soy testigo de Jehová!</t>
+          <t>Hazme conocer tus caminos</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Canción 64</t>
+          <t>Canción 14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Participemos con gozo en la cosecha</t>
+          <t>Honremos al nuevo Rey de la Tierra</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Canción 65</t>
+          <t>Canción 53</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lucha por progresar</t>
+          <t>Hoy voy a salir a predicar</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Canción 66</t>
+          <t>Canción 117</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Proclamemos las buenas noticias</t>
+          <t>Imitemos la bondad de Jehová</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Canción 67</t>
+          <t>Canción 112</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>“Predica la palabra”</t>
+          <t>Jehová, el Dios de la paz</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Canción 68</t>
+          <t>Canción 12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sembremos semillas del Reino</t>
+          <t>Jehová, nuestro gran Dios</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Canción 69</t>
+          <t>Canción 89</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Prediquen las nuevas del Reino</t>
+          <t>Jehová bendice al que escucha y obedece</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Canción 70</t>
+          <t>Canción 7</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Busquemos a los merecedores</t>
+          <t>Jehová es mi fuerza y mi salvación</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Canción 71</t>
+          <t>Canción 4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>¡Somos los guerreros de Jehová!</t>
+          <t>“Jehová es mi Pastor”</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Canción 72</t>
+          <t>Canción 8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Anunciaré la verdad del Reino</t>
+          <t>Jehová es mi Refugio</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Canción 73</t>
+          <t>Canción 148</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Danos fuerzas y valor</t>
+          <t>Jehová es mi Roca de salvación</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Canción 74</t>
+          <t>Canción 9</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ven a cantar la gran canción del Reino</t>
+          <t>¡Jehová es nuestro Rey!</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Canción 75</t>
+          <t>Canción 23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>“¡Aquí estoy, envíame!”</t>
+          <t>Jehová ha empezado su gobierno</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Canción 76</t>
+          <t>Canción 151</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cuéntame lo que sientes</t>
+          <t>Jehová los llamará</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Canción 77</t>
+          <t>Canción 150</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Luz en un mundo oscuro</t>
+          <t>¡Jehová será tu Salvador!</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Canción 78</t>
+          <t>Canción 38</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Enseñemos la Palabra de Dios</t>
+          <t>Jehová te cuidará</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Canción 79</t>
+          <t>Canción 135</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Que sigan firmes en la fe</t>
+          <t>Jehová te pide: “Sé sabio, hijo mío”</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Canción 80</t>
+          <t>Canción 149</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>“Prueben y vean que Jehová es bueno”</t>
+          <t>La canción de la victoria</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Canción 81</t>
+          <t>Canción 19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>La vida del precursor</t>
+          <t>La Cena del Señor</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Canción 82</t>
+          <t>Canción 127</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hagamos que brille nuestra luz</t>
+          <t>La clase de persona que debo ser</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Canción 83</t>
+          <t>Canción 11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>“De casa en casa”</t>
+          <t>La creación alaba a Jehová</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Canción 84</t>
+          <t>Canción 52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Servimos donde se nos necesite</t>
+          <t>La dedicación cristiana</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Canción 85</t>
+          <t>Canción 95</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>“Recíbanse con gusto unos a otros”</t>
+          <t>La luz brilla más cada día</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Canción 86</t>
+          <t>Canción 45</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Necesitamos que Jehová nos enseñe</t>
+          <t>“La meditación de mi corazón”</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Canción 87</t>
+          <t>Canción 62</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ven a recibir ánimo</t>
+          <t>La nueva canción</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Canción 88</t>
+          <t>Canción 42</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hazme conocer tus caminos</t>
+          <t>La oración del siervo de Dios</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Canción 89</t>
+          <t>Canción 113</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jehová bendice al que escucha y obedece</t>
+          <t>La paz del pueblo de Dios</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Canción 90</t>
+          <t>Canción 27</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Animémonos unos a otros</t>
+          <t>La revelación de los hijos de Dios</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Canción 91</t>
+          <t>Canción 1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Una obra de amor</t>
+          <t>Las cualidades principales de Jehová</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Canción 92</t>
+          <t>Canción 98</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Un lugar que lleva tu nombre</t>
+          <t>Las Escrituras están inspiradas por Dios</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Canción 93</t>
+          <t>Canción 5</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bendice nuestras reuniones</t>
+          <t>Las maravillosas obras de Dios</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Canción 94</t>
+          <t>Canción 81</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Agradecidos por la Palabra de Dios</t>
+          <t>La vida del precursor</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Canción 95</t>
+          <t>Canción 131</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>La luz brilla más cada día</t>
+          <t>“Lo que Dios ha unido”</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Canción 96</t>
+          <t>Canción 138</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>El libro de Dios es un tesoro</t>
+          <t>Los cabellos blancos, una hermosa corona</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Canción 97</t>
+          <t>Canción 6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nuestra vida depende de la Palabra de Dios</t>
+          <t>Los cielos proclaman la gloria de Dios</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Canción 98</t>
+          <t>Canción 134</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Las Escrituras están inspiradas por Dios</t>
+          <t>Los hijos son un regalo de Dios</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Canción 99</t>
+          <t>Canción 111</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Miles de fieles hermanos</t>
+          <t>Los motivos de nuestro gozo</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Canción 100</t>
+          <t>Canción 65</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Seamos hospitalarios</t>
+          <t>Lucha por progresar</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Canción 101</t>
+          <t>Canción 77</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sirvamos a Dios en unidad</t>
+          <t>Luz en un mundo oscuro</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Canción 102</t>
+          <t>Canción 122</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ayudemos a los débiles</t>
+          <t>¡Mantengámonos firmes, inmovibles!</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Canción 103</t>
+          <t>Canción 30</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nuestros pastores son un regalo de Dios</t>
+          <t>Mi Amigo, mi Padre, mi Dios</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Canción 104</t>
+          <t>Canción 99</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>El espíritu santo es un regalo de Dios</t>
+          <t>Miles de fieles hermanos</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Canción 105</t>
+          <t>Canción 155</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>“Dios es amor”</t>
+          <t>Mi mayor felicidad</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Canción 106</t>
+          <t>Canción 162</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cultivemos amor verdadero</t>
+          <t>Mi necesidad espiritual</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Canción 107</t>
+          <t>Canción 50</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dios nos enseñó a amar</t>
+          <t>Mi oración de dedicación</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Canción 108</t>
+          <t>Canción 121</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>El amor leal de Jehová</t>
+          <t>Necesitamos autodominio</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Canción 109</t>
+          <t>Canción 86</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amémonos de todo corazón</t>
+          <t>Necesitamos que Jehová nos enseñe</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Canción 110</t>
+          <t>Canción 119</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>El gozo de Jehová</t>
+          <t>Necesitamos una fe fuerte</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Canción 111</t>
+          <t>Canción 144</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Los motivos de nuestro gozo</t>
+          <t>No dejes de mirar allí</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Canción 112</t>
+          <t>Canción 55</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jehová, el Dios de la paz</t>
+          <t>¡No los temas!</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Canción 113</t>
+          <t>Canción 97</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>La paz del pueblo de Dios</t>
+          <t>Nuestra vida depende de la Palabra de Dios</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Canción 114</t>
+          <t>Canción 103</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Demostremos paciencia</t>
+          <t>Nuestros pastores son un regalo de Dios</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Canción 115</t>
+          <t>Canción 47</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Gratitud por la paciencia de Dios</t>
+          <t>Oremos a Dios todos los días</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Canción 116</t>
+          <t>Canción 41</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Seamos amables y bondadosos</t>
+          <t>Padre, escucha mi oración</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Canción 117</t>
+          <t>Canción 64</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Imitemos la bondad de Jehová</t>
+          <t>Participemos con gozo en la cosecha</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Canción 118</t>
+          <t>Canción 32</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>“Danos más fe”</t>
+          <t>¡Ponte de parte de Dios!</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Canción 119</t>
+          <t>Canción 153</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Necesitamos una fe fuerte</t>
+          <t>Por ti seré valiente</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Canción 120</t>
+          <t>Canción 67</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Seamos apacibles y humildes como Cristo</t>
+          <t>“Predica la palabra”</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Canción 121</t>
+          <t>Canción 57</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Necesitamos autodominio</t>
+          <t>Predicamos a toda clase de personas</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Canción 122</t>
+          <t>Canción 69</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>¡Mantengámonos firmes, inmovibles!</t>
+          <t>Prediquen las nuevas del Reino</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Canción 123</t>
+          <t>Canción 66</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Seamos leales y sumisos al orden teocrático</t>
+          <t>Proclamemos las buenas noticias</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Canción 124</t>
+          <t>Canción 80</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Siempre fieles y leales</t>
+          <t>“Prueben y vean que Jehová es bueno”</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Canción 125</t>
+          <t>Canción 136</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Felices los misericordiosos</t>
+          <t>Que Jehová te bendiga</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Canción 126</t>
+          <t>Canción 79</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Siempre fuertes, fieles y firmes</t>
+          <t>Que sigan firmes en la fe</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Canción 127</t>
+          <t>Canción 22</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>La clase de persona que debo ser</t>
+          <t>¡Que venga el Reino que Dios ha establecido!</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Canción 128</t>
+          <t>Canción 17</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Aguantemos hasta el fin</t>
+          <t>“Quiero”</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Canción 129</t>
+          <t>Canción 85</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Servimos con aguante</t>
+          <t>“Recíbanse con gusto unos a otros”</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Canción 130</t>
+          <t>Canción 116</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Aprendamos a perdonar</t>
+          <t>Seamos amables y bondadosos</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Canción 131</t>
+          <t>Canción 120</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>“Lo que Dios ha unido”</t>
+          <t>Seamos apacibles y humildes como Cristo</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Canción 132</t>
+          <t>Canción 100</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ahora ya somos uno</t>
+          <t>Seamos hospitalarios</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Canción 133</t>
+          <t>Canción 123</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sirvamos a Jehová en nuestra juventud</t>
+          <t>Seamos leales y sumisos al orden teocrático</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Canción 134</t>
+          <t>Canción 68</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Los hijos son un regalo de Dios</t>
+          <t>Sembremos semillas del Reino</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Canción 135</t>
+          <t>Canción 129</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jehová te pide: “Sé sabio, hijo mío”</t>
+          <t>Servimos con aguante</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Canción 136</t>
+          <t>Canción 84</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Que Jehová te bendiga</t>
+          <t>Servimos donde se nos necesite</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Canción 137</t>
+          <t>Canción 37</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Fieles, valiosas, amadas</t>
+          <t>Serviré a Jehová con el corazón</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Canción 138</t>
+          <t>Canción 124</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Los cabellos blancos, una hermosa corona</t>
+          <t>Siempre fieles y leales</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Canción 139</t>
+          <t>Canción 126</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>¿Te ves en el nuevo mundo?</t>
+          <t>Siempre fuertes, fieles y firmes</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Canción 140</t>
+          <t>Canción 26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>¡Vida sin fin, al fin!</t>
+          <t>“Si lo haces por él, lo haces por mí”</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Canción 141</t>
+          <t>Canción 101</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>El maravilloso regalo de la vida</t>
+          <t>Sirvamos a Dios en unidad</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Canción 142</t>
+          <t>Canción 133</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Aferrémonos a nuestra esperanza</t>
+          <t>Sirvamos a Jehová en nuestra juventud</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Canción 143</t>
+          <t>Canción 156</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>¡Hay que seguir vigilantes!</t>
+          <t>Si tienes fe</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Canción 144</t>
+          <t>Canción 157</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>No dejes de mirar allí</t>
+          <t>Solo paz</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Canción 145</t>
+          <t>Canción 71</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dios prometió un Paraíso</t>
+          <t>¡Somos los guerreros de Jehová!</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Canción 146</t>
+          <t>Canción 63</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>“Estoy haciendo todo nuevo”</t>
+          <t>¡Soy testigo de Jehová!</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Canción 147</t>
+          <t>Canción 24</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dios nos promete la vida eterna</t>
+          <t>Subamos a la montaña de Jehová</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Canción 148</t>
+          <t>Canción 139</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Jehová es mi Roca de salvación</t>
+          <t>¿Te ves en el nuevo mundo?</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Canción 149</t>
+          <t>Canción 3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>La canción de la victoria</t>
+          <t>Tú me das fuerza, confianza y valor</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Canción 150</t>
+          <t>Canción 2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>¡Jehová será tu Salvador!</t>
+          <t>Tu nombre es Jehová</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Canción 151</t>
+          <t>Canción 154</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Jehová los llamará</t>
+          <t>Un amor sin final</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Canción 152</t>
+          <t>Canción 91</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Un lugar que te honrará</t>
+          <t>Una obra de amor</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Canción 153</t>
+          <t>Canción 43</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Por ti seré valiente</t>
+          <t>Una oración para dar gracias a Dios</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Canción 154</t>
+          <t>Canción 25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Un amor sin final</t>
+          <t>Una posesión especial</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Canción 155</t>
+          <t>Canción 44</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mi mayor felicidad</t>
+          <t>Una súplica ferviente</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Canción 156</t>
+          <t>Canción 39</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Si tienes fe</t>
+          <t>Un buen nombre ante Dios</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Canción 157</t>
+          <t>Canción 92</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Solo paz</t>
+          <t>Un lugar que lleva tu nombre</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Canción 158</t>
+          <t>Canción 152</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Danos paciencia</t>
+          <t>Un lugar que te honrará</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Canción 159</t>
+          <t>Canción 59</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Demos gloria a Jehová</t>
+          <t>Ven a alabar a Jehová</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Canción 160</t>
+          <t>Canción 74</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>¡Buenas noticias!</t>
+          <t>Ven a cantar la gran canción del Reino</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Canción 161</t>
+          <t>Canción 87</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Hacer tu voluntad</t>
+          <t>Ven a recibir ánimo</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Canción 162</t>
+          <t>Canción 140</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mi necesidad espiritual</t>
+          <t>¡Vida sin fin, al fin!</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Canción 56</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Vive la verdad</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Canción 58</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Voy a buscar a los amigos de la paz</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Canción 163</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Ya puedo ver</t>
         </is>
       </c>
     </row>

--- a/Asignaciones/Recursos/canticos_lista.xlsx
+++ b/Asignaciones/Recursos/canticos_lista.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,1964 +429,1956 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Canción 142</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aferrémonos a nuestra esperanza</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Canción 94</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agradecidos por la Palabra de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Canción 142</t>
+          <t>Canción 128</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aferrémonos a nuestra esperanza</t>
+          <t>Aguantemos hasta el fin</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Canción 94</t>
+          <t>Canción 132</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agradecidos por la Palabra de Dios</t>
+          <t>Ahora ya somos uno</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canción 128</t>
+          <t>Canción 16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aguantemos hasta el fin</t>
+          <t>Alabemos a Jehová por su Hijo, el Ungido</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Canción 132</t>
+          <t>Canción 15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ahora ya somos uno</t>
+          <t>Alabemos al Primogénito de Jehová</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Canción 16</t>
+          <t>Canción 10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alabemos a Jehová por su Hijo, el Ungido</t>
+          <t>¡Alabemos a nuestro Dios, Jehová!</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canción 15</t>
+          <t>Canción 49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alabemos al Primogénito de Jehová</t>
+          <t>Alegremos el corazón de Jehová</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canción 10</t>
+          <t>Canción 109</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>¡Alabemos a nuestro Dios, Jehová!</t>
+          <t>Amémonos de todo corazón</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Canción 49</t>
+          <t>Canción 90</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alegremos el corazón de Jehová</t>
+          <t>Animémonos unos a otros</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canción 109</t>
+          <t>Canción 72</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amémonos de todo corazón</t>
+          <t>Anunciaré la verdad del Reino</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Canción 90</t>
+          <t>Canción 130</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Animémonos unos a otros</t>
+          <t>Aprendamos a perdonar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Canción 72</t>
+          <t>Canción 40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anunciaré la verdad del Reino</t>
+          <t>¿A quién servimos?</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Canción 130</t>
+          <t>Canción 75</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aprendamos a perdonar</t>
+          <t>“¡Aquí estoy, envíame!”</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Canción 40</t>
+          <t>Canción 35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>¿A quién servimos?</t>
+          <t>Asegurémonos de lo más importante</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Canción 75</t>
+          <t>Canción 61</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>“¡Aquí estoy, envíame!”</t>
+          <t>¡Avancen, Testigos!</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canción 35</t>
+          <t>Canción 102</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Asegurémonos de lo más importante</t>
+          <t>Ayudemos a los débiles</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canción 61</t>
+          <t>Canción 93</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>¡Avancen, Testigos!</t>
+          <t>Bendice nuestras reuniones</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Canción 102</t>
+          <t>Canción 160</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ayudemos a los débiles</t>
+          <t>¡Buenas noticias!</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canción 93</t>
+          <t>Canción 70</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bendice nuestras reuniones</t>
+          <t>Busquemos a los merecedores</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Canción 160</t>
+          <t>Canción 21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>¡Buenas noticias!</t>
+          <t>Busquemos primero el Reino</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Canción 70</t>
+          <t>Canción 34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Busquemos a los merecedores</t>
+          <t>Caminaré en integridad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Canción 21</t>
+          <t>Canción 31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Busquemos primero el Reino</t>
+          <t>Camina siempre con Jehová</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Canción 34</t>
+          <t>Canción 48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caminaré en integridad</t>
+          <t>Caminemos diariamente con Jehová</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Canción 31</t>
+          <t>Canción 28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camina siempre con Jehová</t>
+          <t>Cómo hacernos amigos de Jehová</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Canción 48</t>
+          <t>Canción 13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caminemos diariamente con Jehová</t>
+          <t>Cristo es nuestro modelo</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Canción 28</t>
+          <t>Canción 76</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cómo hacernos amigos de Jehová</t>
+          <t>Cuéntame lo que sientes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canción 13</t>
+          <t>Canción 36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cristo es nuestro modelo</t>
+          <t>Cuidemos nuestro corazón</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Canción 76</t>
+          <t>Canción 106</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cuéntame lo que sientes</t>
+          <t>Cultivemos amor verdadero</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Canción 36</t>
+          <t>Canción 73</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cuidemos nuestro corazón</t>
+          <t>Danos fuerzas y valor</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Canción 106</t>
+          <t>Canción 118</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cultivemos amor verdadero</t>
+          <t>“Danos más fe”</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Canción 73</t>
+          <t>Canción 158</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Danos fuerzas y valor</t>
+          <t>Danos paciencia</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Canción 118</t>
+          <t>Canción 83</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>“Danos más fe”</t>
+          <t>“De casa en casa”</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Canción 158</t>
+          <t>Canción 159</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Danos paciencia</t>
+          <t>Demos gloria a Jehová</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Canción 83</t>
+          <t>Canción 114</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>“De casa en casa”</t>
+          <t>Demostremos paciencia</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Canción 159</t>
+          <t>Canción 105</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Demos gloria a Jehová</t>
+          <t>“Dios es amor”</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Canción 114</t>
+          <t>Canción 107</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Demostremos paciencia</t>
+          <t>Dios nos enseñó a amar</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Canción 105</t>
+          <t>Canción 147</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>“Dios es amor”</t>
+          <t>Dios nos promete la vida eterna</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Canción 107</t>
+          <t>Canción 145</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dios nos enseñó a amar</t>
+          <t>Dios prometió un Paraíso</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Canción 147</t>
+          <t>Canción 33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dios nos promete la vida eterna</t>
+          <t>Echa sobre Dios tu carga</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Canción 145</t>
+          <t>Canción 108</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dios prometió un Paraíso</t>
+          <t>El amor leal de Jehová</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Canción 33</t>
+          <t>Canción 104</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Echa sobre Dios tu carga</t>
+          <t>El espíritu santo es un regalo de Dios</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Canción 108</t>
+          <t>Canción 110</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>El amor leal de Jehová</t>
+          <t>El gozo de Jehová</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Canción 104</t>
+          <t>Canción 96</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>El espíritu santo es un regalo de Dios</t>
+          <t>El libro de Dios es un tesoro</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Canción 110</t>
+          <t>Canción 141</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>El gozo de Jehová</t>
+          <t>El maravilloso regalo de la vida</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Canción 96</t>
+          <t>Canción 78</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>El libro de Dios es un tesoro</t>
+          <t>Enseñemos la Palabra de Dios</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Canción 141</t>
+          <t>Canción 20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>El maravilloso regalo de la vida</t>
+          <t>Enviaste a Jesús, tu Hijo amado</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Canción 78</t>
+          <t>Canción 51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Enseñemos la Palabra de Dios</t>
+          <t>Estamos dedicados a Dios</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Canción 20</t>
+          <t>Canción 54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Enviaste a Jesús, tu Hijo amado</t>
+          <t>“Este es el camino”</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Canción 51</t>
+          <t>Canción 146</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Estamos dedicados a Dios</t>
+          <t>“Estoy haciendo todo nuevo”</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Canción 54</t>
+          <t>Canción 125</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>“Este es el camino”</t>
+          <t>Felices los misericordiosos</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Canción 146</t>
+          <t>Canción 137</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>“Estoy haciendo todo nuevo”</t>
+          <t>Fieles, valiosas, amadas</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Canción 125</t>
+          <t>Canción 46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Felices los misericordiosos</t>
+          <t>Gracias, Jehová</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Canción 137</t>
+          <t>Canción 18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fieles, valiosas, amadas</t>
+          <t>Gracias por el rescate</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Canción 46</t>
+          <t>Canción 115</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gracias, Jehová</t>
+          <t>Gratitud por la paciencia de Dios</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Canción 18</t>
+          <t>Canción 161</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gracias por el rescate</t>
+          <t>Hacer tu voluntad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Canción 115</t>
+          <t>Canción 29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gratitud por la paciencia de Dios</t>
+          <t>Hagamos honor a nuestro nombre</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Canción 161</t>
+          <t>Canción 82</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hacer tu voluntad</t>
+          <t>Hagamos que brille nuestra luz</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Canción 29</t>
+          <t>Canción 143</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hagamos honor a nuestro nombre</t>
+          <t>¡Hay que seguir vigilantes!</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Canción 82</t>
+          <t>Canción 60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hagamos que brille nuestra luz</t>
+          <t>Hay vidas en juego</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Canción 143</t>
+          <t>Canción 88</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>¡Hay que seguir vigilantes!</t>
+          <t>Hazme conocer tus caminos</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Canción 60</t>
+          <t>Canción 14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hay vidas en juego</t>
+          <t>Honremos al nuevo Rey de la Tierra</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Canción 88</t>
+          <t>Canción 53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hazme conocer tus caminos</t>
+          <t>Hoy voy a salir a predicar</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Canción 14</t>
+          <t>Canción 117</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Honremos al nuevo Rey de la Tierra</t>
+          <t>Imitemos la bondad de Jehová</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Canción 53</t>
+          <t>Canción 112</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hoy voy a salir a predicar</t>
+          <t>Jehová, el Dios de la paz</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Canción 117</t>
+          <t>Canción 12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Imitemos la bondad de Jehová</t>
+          <t>Jehová, nuestro gran Dios</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Canción 112</t>
+          <t>Canción 89</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jehová, el Dios de la paz</t>
+          <t>Jehová bendice al que escucha y obedece</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Canción 12</t>
+          <t>Canción 7</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jehová, nuestro gran Dios</t>
+          <t>Jehová es mi fuerza y mi salvación</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Canción 89</t>
+          <t>Canción 4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jehová bendice al que escucha y obedece</t>
+          <t>“Jehová es mi Pastor”</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Canción 7</t>
+          <t>Canción 8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jehová es mi fuerza y mi salvación</t>
+          <t>Jehová es mi Refugio</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Canción 4</t>
+          <t>Canción 148</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>“Jehová es mi Pastor”</t>
+          <t>Jehová es mi Roca de salvación</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Canción 8</t>
+          <t>Canción 9</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jehová es mi Refugio</t>
+          <t>¡Jehová es nuestro Rey!</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Canción 148</t>
+          <t>Canción 23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jehová es mi Roca de salvación</t>
+          <t>Jehová ha empezado su gobierno</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Canción 9</t>
+          <t>Canción 151</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>¡Jehová es nuestro Rey!</t>
+          <t>Jehová los llamará</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Canción 23</t>
+          <t>Canción 150</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jehová ha empezado su gobierno</t>
+          <t>¡Jehová será tu Salvador!</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Canción 151</t>
+          <t>Canción 38</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jehová los llamará</t>
+          <t>Jehová te cuidará</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Canción 150</t>
+          <t>Canción 135</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>¡Jehová será tu Salvador!</t>
+          <t>Jehová te pide: “Sé sabio, hijo mío”</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Canción 38</t>
+          <t>Canción 149</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jehová te cuidará</t>
+          <t>La canción de la victoria</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Canción 135</t>
+          <t>Canción 19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jehová te pide: “Sé sabio, hijo mío”</t>
+          <t>La Cena del Señor</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Canción 149</t>
+          <t>Canción 127</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>La canción de la victoria</t>
+          <t>La clase de persona que debo ser</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Canción 19</t>
+          <t>Canción 11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>La Cena del Señor</t>
+          <t>La creación alaba a Jehová</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Canción 127</t>
+          <t>Canción 52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>La clase de persona que debo ser</t>
+          <t>La dedicación cristiana</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Canción 11</t>
+          <t>Canción 95</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>La creación alaba a Jehová</t>
+          <t>La luz brilla más cada día</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Canción 52</t>
+          <t>Canción 45</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>La dedicación cristiana</t>
+          <t>“La meditación de mi corazón”</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Canción 95</t>
+          <t>Canción 62</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>La luz brilla más cada día</t>
+          <t>La nueva canción</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Canción 45</t>
+          <t>Canción 42</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>“La meditación de mi corazón”</t>
+          <t>La oración del siervo de Dios</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Canción 62</t>
+          <t>Canción 113</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>La nueva canción</t>
+          <t>La paz del pueblo de Dios</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Canción 42</t>
+          <t>Canción 27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>La oración del siervo de Dios</t>
+          <t>La revelación de los hijos de Dios</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Canción 113</t>
+          <t>Canción 1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>La paz del pueblo de Dios</t>
+          <t>Las cualidades principales de Jehová</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Canción 27</t>
+          <t>Canción 98</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>La revelación de los hijos de Dios</t>
+          <t>Las Escrituras están inspiradas por Dios</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Canción 1</t>
+          <t>Canción 5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Las cualidades principales de Jehová</t>
+          <t>Las maravillosas obras de Dios</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Canción 98</t>
+          <t>Canción 81</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Las Escrituras están inspiradas por Dios</t>
+          <t>La vida del precursor</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Canción 5</t>
+          <t>Canción 131</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Las maravillosas obras de Dios</t>
+          <t>“Lo que Dios ha unido”</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Canción 81</t>
+          <t>Canción 138</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>La vida del precursor</t>
+          <t>Los cabellos blancos, una hermosa corona</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Canción 131</t>
+          <t>Canción 6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>“Lo que Dios ha unido”</t>
+          <t>Los cielos proclaman la gloria de Dios</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Canción 138</t>
+          <t>Canción 134</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Los cabellos blancos, una hermosa corona</t>
+          <t>Los hijos son un regalo de Dios</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Canción 6</t>
+          <t>Canción 111</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Los cielos proclaman la gloria de Dios</t>
+          <t>Los motivos de nuestro gozo</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Canción 134</t>
+          <t>Canción 65</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Los hijos son un regalo de Dios</t>
+          <t>Lucha por progresar</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Canción 111</t>
+          <t>Canción 77</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Los motivos de nuestro gozo</t>
+          <t>Luz en un mundo oscuro</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Canción 65</t>
+          <t>Canción 122</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lucha por progresar</t>
+          <t>¡Mantengámonos firmes, inmovibles!</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Canción 77</t>
+          <t>Canción 30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Luz en un mundo oscuro</t>
+          <t>Mi Amigo, mi Padre, mi Dios</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Canción 122</t>
+          <t>Canción 99</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>¡Mantengámonos firmes, inmovibles!</t>
+          <t>Miles de fieles hermanos</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Canción 30</t>
+          <t>Canción 155</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mi Amigo, mi Padre, mi Dios</t>
+          <t>Mi mayor felicidad</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Canción 99</t>
+          <t>Canción 162</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Miles de fieles hermanos</t>
+          <t>Mi necesidad espiritual</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Canción 155</t>
+          <t>Canción 50</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mi mayor felicidad</t>
+          <t>Mi oración de dedicación</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Canción 162</t>
+          <t>Canción 121</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mi necesidad espiritual</t>
+          <t>Necesitamos autodominio</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Canción 50</t>
+          <t>Canción 86</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mi oración de dedicación</t>
+          <t>Necesitamos que Jehová nos enseñe</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Canción 121</t>
+          <t>Canción 119</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Necesitamos autodominio</t>
+          <t>Necesitamos una fe fuerte</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Canción 86</t>
+          <t>Canción 144</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Necesitamos que Jehová nos enseñe</t>
+          <t>No dejes de mirar allí</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Canción 119</t>
+          <t>Canción 55</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Necesitamos una fe fuerte</t>
+          <t>¡No los temas!</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Canción 144</t>
+          <t>Canción 97</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>No dejes de mirar allí</t>
+          <t>Nuestra vida depende de la Palabra de Dios</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Canción 55</t>
+          <t>Canción 103</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>¡No los temas!</t>
+          <t>Nuestros pastores son un regalo de Dios</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Canción 97</t>
+          <t>Canción 47</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nuestra vida depende de la Palabra de Dios</t>
+          <t>Oremos a Dios todos los días</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Canción 103</t>
+          <t>Canción 41</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nuestros pastores son un regalo de Dios</t>
+          <t>Padre, escucha mi oración</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Canción 47</t>
+          <t>Canción 64</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Oremos a Dios todos los días</t>
+          <t>Participemos con gozo en la cosecha</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Canción 41</t>
+          <t>Canción 32</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Padre, escucha mi oración</t>
+          <t>¡Ponte de parte de Dios!</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Canción 64</t>
+          <t>Canción 153</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Participemos con gozo en la cosecha</t>
+          <t>Por ti seré valiente</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Canción 32</t>
+          <t>Canción 67</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>¡Ponte de parte de Dios!</t>
+          <t>“Predica la palabra”</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Canción 153</t>
+          <t>Canción 57</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Por ti seré valiente</t>
+          <t>Predicamos a toda clase de personas</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Canción 67</t>
+          <t>Canción 69</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>“Predica la palabra”</t>
+          <t>Prediquen las nuevas del Reino</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Canción 57</t>
+          <t>Canción 66</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Predicamos a toda clase de personas</t>
+          <t>Proclamemos las buenas noticias</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Canción 69</t>
+          <t>Canción 80</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Prediquen las nuevas del Reino</t>
+          <t>“Prueben y vean que Jehová es bueno”</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Canción 66</t>
+          <t>Canción 136</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Proclamemos las buenas noticias</t>
+          <t>Que Jehová te bendiga</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Canción 80</t>
+          <t>Canción 79</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>“Prueben y vean que Jehová es bueno”</t>
+          <t>Que sigan firmes en la fe</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Canción 136</t>
+          <t>Canción 22</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Que Jehová te bendiga</t>
+          <t>¡Que venga el Reino que Dios ha establecido!</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Canción 79</t>
+          <t>Canción 17</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Que sigan firmes en la fe</t>
+          <t>“Quiero”</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Canción 22</t>
+          <t>Canción 85</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>¡Que venga el Reino que Dios ha establecido!</t>
+          <t>“Recíbanse con gusto unos a otros”</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Canción 17</t>
+          <t>Canción 116</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>“Quiero”</t>
+          <t>Seamos amables y bondadosos</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Canción 85</t>
+          <t>Canción 120</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>“Recíbanse con gusto unos a otros”</t>
+          <t>Seamos apacibles y humildes como Cristo</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Canción 116</t>
+          <t>Canción 100</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Seamos amables y bondadosos</t>
+          <t>Seamos hospitalarios</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Canción 120</t>
+          <t>Canción 123</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Seamos apacibles y humildes como Cristo</t>
+          <t>Seamos leales y sumisos al orden teocrático</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Canción 100</t>
+          <t>Canción 68</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Seamos hospitalarios</t>
+          <t>Sembremos semillas del Reino</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Canción 123</t>
+          <t>Canción 129</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Seamos leales y sumisos al orden teocrático</t>
+          <t>Servimos con aguante</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Canción 68</t>
+          <t>Canción 84</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sembremos semillas del Reino</t>
+          <t>Servimos donde se nos necesite</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Canción 129</t>
+          <t>Canción 37</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Servimos con aguante</t>
+          <t>Serviré a Jehová con el corazón</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Canción 84</t>
+          <t>Canción 124</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Servimos donde se nos necesite</t>
+          <t>Siempre fieles y leales</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Canción 37</t>
+          <t>Canción 126</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Serviré a Jehová con el corazón</t>
+          <t>Siempre fuertes, fieles y firmes</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Canción 124</t>
+          <t>Canción 26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Siempre fieles y leales</t>
+          <t>“Si lo haces por él, lo haces por mí”</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Canción 126</t>
+          <t>Canción 101</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Siempre fuertes, fieles y firmes</t>
+          <t>Sirvamos a Dios en unidad</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Canción 26</t>
+          <t>Canción 133</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>“Si lo haces por él, lo haces por mí”</t>
+          <t>Sirvamos a Jehová en nuestra juventud</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Canción 101</t>
+          <t>Canción 156</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sirvamos a Dios en unidad</t>
+          <t>Si tienes fe</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Canción 133</t>
+          <t>Canción 157</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sirvamos a Jehová en nuestra juventud</t>
+          <t>Solo paz</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Canción 156</t>
+          <t>Canción 71</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Si tienes fe</t>
+          <t>¡Somos los guerreros de Jehová!</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Canción 157</t>
+          <t>Canción 63</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Solo paz</t>
+          <t>¡Soy testigo de Jehová!</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Canción 71</t>
+          <t>Canción 24</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>¡Somos los guerreros de Jehová!</t>
+          <t>Subamos a la montaña de Jehová</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Canción 63</t>
+          <t>Canción 139</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>¡Soy testigo de Jehová!</t>
+          <t>¿Te ves en el nuevo mundo?</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Canción 24</t>
+          <t>Canción 3</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Subamos a la montaña de Jehová</t>
+          <t>Tú me das fuerza, confianza y valor</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Canción 139</t>
+          <t>Canción 2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>¿Te ves en el nuevo mundo?</t>
+          <t>Tu nombre es Jehová</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Canción 3</t>
+          <t>Canción 154</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Tú me das fuerza, confianza y valor</t>
+          <t>Un amor sin final</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Canción 2</t>
+          <t>Canción 91</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Tu nombre es Jehová</t>
+          <t>Una obra de amor</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Canción 154</t>
+          <t>Canción 43</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Un amor sin final</t>
+          <t>Una oración para dar gracias a Dios</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Canción 91</t>
+          <t>Canción 25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Una obra de amor</t>
+          <t>Una posesión especial</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Canción 43</t>
+          <t>Canción 44</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Una oración para dar gracias a Dios</t>
+          <t>Una súplica ferviente</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Canción 25</t>
+          <t>Canción 39</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Una posesión especial</t>
+          <t>Un buen nombre ante Dios</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Canción 44</t>
+          <t>Canción 92</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Una súplica ferviente</t>
+          <t>Un lugar que lleva tu nombre</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Canción 39</t>
+          <t>Canción 152</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Un buen nombre ante Dios</t>
+          <t>Un lugar que te honrará</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Canción 92</t>
+          <t>Canción 59</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Un lugar que lleva tu nombre</t>
+          <t>Ven a alabar a Jehová</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Canción 152</t>
+          <t>Canción 74</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Un lugar que te honrará</t>
+          <t>Ven a cantar la gran canción del Reino</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Canción 59</t>
+          <t>Canción 87</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ven a alabar a Jehová</t>
+          <t>Ven a recibir ánimo</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Canción 74</t>
+          <t>Canción 140</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ven a cantar la gran canción del Reino</t>
+          <t>¡Vida sin fin, al fin!</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Canción 87</t>
+          <t>Canción 56</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ven a recibir ánimo</t>
+          <t>Vive la verdad</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Canción 140</t>
+          <t>Canción 58</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>¡Vida sin fin, al fin!</t>
+          <t>Voy a buscar a los amigos de la paz</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Canción 56</t>
+          <t>Canción 163</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
-        <is>
-          <t>Vive la verdad</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Canción 58</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Voy a buscar a los amigos de la paz</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Canción 163</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
         <is>
           <t>Ya puedo ver</t>
         </is>
